--- a/团队需求明细.xlsx
+++ b/团队需求明细.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +35,27 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <color rgb="00375623"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -56,8 +76,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -91,9 +135,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,11 +517,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -550,7 +608,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>基础功能版本</t>
+          <t>基础功能版本-支付通道接入</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -565,7 +623,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -583,7 +641,7 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -595,44 +653,44 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>AB-CRPS1.0.2_102</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>优化功能</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>优化对账逻辑，提升准确性</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>田家喜</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>李靖钦</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>对公运营支付</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>常规版</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>优化版</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -640,7 +698,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
@@ -654,7 +712,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>新增功能</t>
+          <t>新增银企直连功能</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -669,7 +727,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>刘强</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -687,66 +745,586 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.0.4_104</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>批量代发功能优化</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>陈明</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.1.0_201</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>新增电子回单功能</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>赵雪</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.0.4_104</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>性能优化</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.1.1_202</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>支付限额调整功能</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>田家喜</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>李靖钦</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>孙鹏</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>对公运营支付</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>待开始</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.1.2_203</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>手续费自动计算</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>周婷</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.2.0_301</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>跨境支付功能一期</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>吴昊</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.2.1_302</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>汇率自动转换</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>郑好</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.3.0_401</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>财务对账自动化</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>冯博</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.0_501</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>架构升级-微服务改造</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>林峰</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.1_502</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>数据库分库分表</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>高健</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.0_601</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>实时支付监控系统</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>肖丽</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.1_602</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>异常交易自动预警</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>许洋</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
         </is>
       </c>
     </row>
@@ -756,4 +1334,131 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>需求统计汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>总需求数</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/团队需求明细.xlsx
+++ b/团队需求明细.xlsx
@@ -29,7 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>团队需求明细 - AB-CRPS系统</t>
+          <t>团队需求明细 - AB-CRPS系统 - 基础中台研发中心-支付运营研发团队</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -811,12 +811,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.0_201</t>
+          <t>AB-CRPS1.0.5_105</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>新增电子回单功能</t>
+          <t>支付凭证电子化</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -849,26 +849,26 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.1_202</t>
+          <t>AB-CRPS1.0.6_106</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>支付限额调整功能</t>
+          <t>交易流水查询优化</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -898,29 +898,29 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.2_203</t>
+          <t>AB-CRPS1.1.0_201</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>手续费自动计算</t>
+          <t>新增电子回单功能</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -953,26 +953,26 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.0_301</t>
+          <t>AB-CRPS1.1.1_202</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>跨境支付功能一期</t>
+          <t>支付限额调整功能</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>跨境支付</t>
+          <t>对公运营支付</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1005,26 +1005,26 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.1_302</t>
+          <t>AB-CRPS1.1.2_203</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>汇率自动转换</t>
+          <t>手续费自动计算</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>跨境支付</t>
+          <t>对公运营支付</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1057,26 +1057,26 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.0_401</t>
+          <t>AB-CRPS1.1.3_204</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>财务对账自动化</t>
+          <t>企业钱包功能上线</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>企业钱包</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1106,29 +1106,29 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.0_501</t>
+          <t>AB-CRPS1.1.4_205</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>架构升级-微服务改造</t>
+          <t>退款流程自动化</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>对公运营支付</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1158,29 +1158,29 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.1_502</t>
+          <t>AB-CRPS1.2.0_301</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>数据库分库分表</t>
+          <t>跨境支付功能一期</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1210,29 +1210,29 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.0_601</t>
+          <t>AB-CRPS1.2.1_302</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>实时支付监控系统</t>
+          <t>汇率自动转换</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1265,66 +1265,1158 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.1_602</t>
+          <t>AB-CRPS1.2.2_303</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>跨境付款申报</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>许洋</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.2.3_304</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>多币种结算支持</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>徐鹏</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.3.0_401</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>财务对账自动化</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>孙浩</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.3.1_402</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>银行回单自动匹配</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>马超</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.3.2_403</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>账期自动清分</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>韩梅</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.3.3_404</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>财务报表自动生成</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>对公运营支付</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.4.0_501</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>API开放平台一期</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>朱磊</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.4.1_502</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>第三方支付接入</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>秦奋</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.4.2_503</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>SDK开发者工具包</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>尤佳</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.5.0_601</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>移动端支付优化</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>许珂</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.5.1_602</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>APP指纹支付</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>西门吹</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.5.2_603</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>支付码动态更新</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>欧阳峰</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.0_701</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>架构升级-微服务改造</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>司马光</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.1_702</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>数据库分库分表</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>诸葛亮</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.2_703</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>消息队列异步化</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>貂蝉</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.0_801</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>实时支付监控系统</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>吕布</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.1_802</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>异常交易自动预警</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>许洋</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>关羽</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>运维支持</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>2027-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.2_803</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>支付成功率监控</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>张飞</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2027-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.3_804</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>银行通道质量分析</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>刘备</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_901</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>智能路由优化</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>曹操</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.1_902</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>通道自动切换</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>孙权</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>2027-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.2_903</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>成本最优通道选择</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>李靖钦</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>周瑜</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2027-07-01</t>
         </is>
       </c>
     </row>
@@ -1345,7 +2437,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1375,7 +2467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -1385,7 +2477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1395,7 +2487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1405,7 +2497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1415,7 +2507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1425,7 +2517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1435,7 +2527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1445,7 +2537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1455,7 +2547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/团队需求明细.xlsx
+++ b/团队需求明细.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,23 +29,35 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="009C5700"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="001F4E79"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00375623"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,9 +65,13 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -76,14 +92,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF6B6B"/>
+        <bgColor rgb="00FF6B6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE66D"/>
+        <bgColor rgb="00FFE66D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004ECDC4"/>
+        <bgColor rgb="004ECDC4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,35 +163,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,22 +570,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>团队需求明细 - AB-CRPS系统 - 基础中台研发中心-支付运营研发团队</t>
@@ -547,8 +606,14 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="25" customHeight="1">
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>版本名称</t>
@@ -556,7 +621,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>版本描述</t>
+          <t>需求描述</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -566,17 +631,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>创建人</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>团队</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>业务领域</t>
+          <t>业务域</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -586,17 +651,47 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
           <t>需求类型</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>计划投产时间</t>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>预估工时(h)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>实际工时(h)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>计划投产</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>实际投产</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -618,17 +713,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>支付一组</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -636,71 +731,123 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>2025-07-10</t>
         </is>
       </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>提前完成</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>AB-CRPS1.0.2_102</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>优化对账逻辑，提升准确性</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="L4" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>略有延期</t>
         </is>
       </c>
     </row>
@@ -722,17 +869,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>刘强</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -740,73 +887,121 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>银企接口调整</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>AB-CRPS1.0.4_104</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>批量代发功能优化</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>陈明</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="L6" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -826,17 +1021,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>赵雪</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>赵雪</t>
+          <t>支付一组</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -844,73 +1039,117 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>AB-CRPS1.0.6_106</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>交易流水查询优化</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>孙鹏</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="L8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -930,17 +1169,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>周婷</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>周婷</t>
+          <t>支付一组</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -948,71 +1187,119 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>AB-CRPS1.1.1_202</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>支付限额调整功能</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>吴昊</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="L10" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>配置复杂</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1321,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>郑好</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>郑好</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1052,71 +1339,123 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>费率规则复杂</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>AB-CRPS1.1.3_204</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>企业钱包功能上线</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>冯博</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>企业钱包</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="L12" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>涉及资金安全</t>
         </is>
       </c>
     </row>
@@ -1138,17 +1477,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>林峰</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>林峰</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>对公运营支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1156,499 +1495,685 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.2.0_301</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>跨境支付功能一期</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.1.5_206</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>账户冻结解冻功能</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>高健</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>跨境支付</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>AB-CRPS1.2.0_301</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付功能一期</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>肖丽</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>重点需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>AB-CRPS1.2.1_302</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>汇率自动转换</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>肖丽</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>许洋</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>跨境支付</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="L16" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.2.2_303</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>跨境付款申报</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>许洋</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>跨境支付</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>AB-CRPS1.2.2_303</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>跨境付款申报</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>徐鹏</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>监管合规</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>AB-CRPS1.2.3_304</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>多币种结算支持</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>徐鹏</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>孙浩</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>跨境支付</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="L18" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.3.0_401</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>财务对账自动化</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>孙浩</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>AB-CRPS1.3.0_401</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>财务对账自动化</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>马超</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>AB-CRPS1.3.1_402</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>银行回单自动匹配</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>马超</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>韩梅</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="L20" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.3.2_403</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>账期自动清分</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>韩梅</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>AB-CRPS1.3.2_403</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>账期自动清分</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>AB-CRPS1.3.3_404</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>财务报表自动生成</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>杨明</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>对公运营支付</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>朱磊</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="L22" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.4.0_501</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>API开放平台一期</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>朱磊</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>开放平台</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.4.1_502</t>
+          <t>AB-CRPS1.3.4_405</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>第三方支付接入</t>
+          <t>发票自动开具</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1658,101 +2183,137 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>秦奋</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>秦奋</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.4.0_501</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>API开放平台一期</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>尤佳</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
           <t>开放平台</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.4.2_503</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>SDK开发者工具包</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>尤佳</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>开放平台</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+      <c r="L24" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>重要项目</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.0_601</t>
+          <t>AB-CRPS1.4.1_502</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>移动端支付优化</t>
+          <t>第三方支付接入</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1762,17 +2323,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>许珂</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>许珂</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>移动支付</t>
+          <t>开放平台</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1780,83 +2341,119 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
+      <c r="L25" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>支付宝/微信</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS1.5.1_602</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>APP指纹支付</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.4.2_503</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SDK开发者工具包</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>西门吹</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>移动支付</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
-        </is>
-      </c>
+      <c r="L26" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.2_603</t>
+          <t>AB-CRPS1.4.3_504</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>支付码动态更新</t>
+          <t>API文档自动化</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1866,101 +2463,133 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>欧阳峰</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>欧阳峰</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.5.0_601</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>移动端支付优化</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>司马光</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
           <t>移动支付</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>待开发</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS2.0.0_701</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>架构升级-微服务改造</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>司马光</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>技术重构</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
+      <c r="L28" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.1_702</t>
+          <t>AB-CRPS1.5.1_602</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>数据库分库分表</t>
+          <t>APP指纹支付</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1970,17 +2599,17 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>诸葛亮</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>诸葛亮</t>
+          <t>移动组</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>移动支付</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1988,83 +2617,119 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>生物识别</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS2.0.2_703</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>消息队列异步化</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS1.5.2_603</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>支付码动态更新</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>貂蝉</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>技术重构</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.0_801</t>
+          <t>AB-CRPS1.5.3_604</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>实时支付监控系统</t>
+          <t>离线支付支持</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2074,17 +2739,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>吕布</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>吕布</t>
+          <t>移动组</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>移动支付</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2092,83 +2757,123 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>2027-01-10</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>技术挑战大</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.0_701</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>架构升级-微服务改造</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>关羽</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS2.1.1_802</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>异常交易自动预警</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>关羽</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>运维支持</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>规划中</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>2027-04-15</t>
+      <c r="L32" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>重大重构</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.2_803</t>
+          <t>AB-CRPS2.0.1_702</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>支付成功率监控</t>
+          <t>数据库分库分表</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2178,17 +2883,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>张飞</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>张飞</t>
+          <t>架构组</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>技术重构</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2196,83 +2901,119 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>2027-05-01</t>
-        </is>
-      </c>
+      <c r="L33" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS2.1.3_804</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>银行通道质量分析</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.0.2_703</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>消息队列异步化</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>运维支持</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>2027-05-15</t>
+      <c r="L34" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>Kafka迁移</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.2.0_901</t>
+          <t>AB-CRPS2.0.3_704</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>智能路由优化</t>
+          <t>缓存架构优化</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2282,17 +3023,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>李靖钦</t>
+          <t>曹操</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>曹操</t>
+          <t>架构组</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>算法优化</t>
+          <t>技术重构</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -2300,129 +3041,529 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>2027-06-01</t>
+      <c r="L35" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Redis集群</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS2.2.1_902</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>通道自动切换</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.0_801</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>实时支付监控系统</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>孙权</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>算法优化</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>常规版</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>2027-06-15</t>
-        </is>
-      </c>
+      <c r="L36" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>AB-CRPS2.1.1_802</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>异常交易自动预警</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>周瑜</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>2027-04-15</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>风控相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.2_803</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>支付成功率监控</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>鲁智深</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-01</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr"/>
+      <c r="P38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.1.3_804</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>银行通道质量分析</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>武松</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_901</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>智能路由优化</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>林冲</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.1_902</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>通道自动切换</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>宋江</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>2027-06-15</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
           <t>AB-CRPS2.2.2_903</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>成本最优通道选择</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>田家喜</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>李靖钦</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>周瑜</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>吴用</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>算法优化</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>AB-CRPS</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>优化版</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="L42" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>2027-07-01</t>
         </is>
       </c>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2434,40 +3575,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>需求统计汇总</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>状态分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>总需求数</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>36</v>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>预估工时</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2479,6 +3623,9 @@
       <c r="B5" t="n">
         <v>12</v>
       </c>
+      <c r="C5" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2489,6 +3636,9 @@
       <c r="B6" t="n">
         <v>3</v>
       </c>
+      <c r="C6" t="n">
+        <v>380</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2497,7 +3647,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1105</v>
       </c>
     </row>
     <row r="8">
@@ -2507,50 +3660,184 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>12</v>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>优先级分布</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>团队分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>团队</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>需求数</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/团队需求明细.xlsx
+++ b/团队需求明细.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工时统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,14 +62,19 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="004472C4"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="13">
@@ -163,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,7 +210,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -570,11 +577,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -698,12 +705,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.1_101</t>
+          <t>AB-CRPS1.1.0_101</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>基础功能版本-支付通道接入</t>
+          <t>跨境付款申报</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -713,17 +720,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>开发03</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>跨境组</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>技术重构</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -738,7 +745,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -752,36 +759,36 @@
         </is>
       </c>
       <c r="L3" s="4" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>提前完成</t>
+          <t>略有延期</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.2_102</t>
+          <t>AB-CRPS1.1.0_102</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>优化对账逻辑，提升准确性</t>
+          <t>人脸支付</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -791,17 +798,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>开发09</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>算法优化</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -809,19 +816,19 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
+          <t>常规版</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -830,36 +837,36 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>略有延期</t>
+          <t>需求变更</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.3_103</t>
+          <t>AB-CRPS1.1.0_103</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>新增银企直连功能</t>
+          <t>反洗钱监控</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -869,12 +876,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>开发16</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>支付二组</t>
+          <t>架构组</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -894,7 +901,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -908,36 +915,36 @@
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>银企接口调整</t>
+          <t>略有延期</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.4_104</t>
+          <t>AB-CRPS1.1.0_104</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>批量代发功能优化</t>
+          <t>合规检查</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -947,17 +954,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>陈明</t>
+          <t>开发07</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>支付二组</t>
+          <t>算法组</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -972,7 +979,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -986,19 +993,19 @@
         </is>
       </c>
       <c r="L6" s="7" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr"/>
@@ -1006,12 +1013,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.5_105</t>
+          <t>AB-CRPS1.1.0_105</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>支付凭证电子化</t>
+          <t>异常交易预警</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1021,17 +1028,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>赵雪</t>
+          <t>开发13</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>算法优化</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1039,14 +1046,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1060,32 +1067,36 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>略有延期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.0.6_106</t>
+          <t>AB-CRPS1.1.0_106</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>交易流水查询优化</t>
+          <t>容灾切换</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1095,12 +1106,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>孙鹏</t>
+          <t>开发11</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>支付三组</t>
+          <t>移动组</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1113,14 +1124,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1134,19 +1145,19 @@
         </is>
       </c>
       <c r="L8" s="7" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr"/>
@@ -1154,12 +1165,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.0_201</t>
+          <t>AB-CRPS1.1.0_107</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>新增电子回单功能</t>
+          <t>账户管理功能</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1169,7 +1180,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>周婷</t>
+          <t>开发16</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1179,7 +1190,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>企业钱包</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1187,19 +1198,19 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
+          <t>优化版</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1208,32 +1219,36 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>提前完成</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.1_202</t>
+          <t>AB-CRPS1.1.0_108</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>支付限额调整功能</t>
+          <t>智能路由算法</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1243,17 +1258,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>吴昊</t>
+          <t>开发03</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>支付二组</t>
+          <t>架构组</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>风控合规</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -1282,36 +1297,32 @@
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>配置复杂</t>
-        </is>
-      </c>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.2_203</t>
+          <t>AB-CRPS1.1.0_109</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>手续费自动计算</t>
+          <t>银企直连功能</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1321,12 +1332,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>郑好</t>
+          <t>开发05</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>支付三组</t>
+          <t>跨境组</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1339,19 +1350,19 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
+          <t>重构版</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1360,36 +1371,32 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>费率规则复杂</t>
-        </is>
-      </c>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.3_204</t>
+          <t>AB-CRPS1.1.0_110</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>企业钱包功能上线</t>
+          <t>交易监控预警</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1399,17 +1406,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>冯博</t>
+          <t>开发13</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>企业钱包</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1417,9 +1424,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1429,7 +1436,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>常规版</t>
+          <t>重构版</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1438,36 +1445,32 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>涉及资金安全</t>
-        </is>
-      </c>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.4_205</t>
+          <t>AB-CRPS1.2.0_111</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>退款流程自动化</t>
+          <t>账户管理功能</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1477,17 +1480,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>林峰</t>
+          <t>开发17</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>支付二组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>企业钱包</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1495,14 +1498,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1516,32 +1519,36 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>略有延期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.1.5_206</t>
+          <t>AB-CRPS1.2.0_112</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>账户冻结解冻功能</t>
+          <t>交易监控预警</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1551,17 +1558,17 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>高健</t>
+          <t>开发20</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>支付三组</t>
+          <t>风控组</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>企业钱包</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -1569,9 +1576,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1581,7 +1588,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>常规版</t>
+          <t>重构版</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1590,19 +1597,19 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr"/>
@@ -1610,12 +1617,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.0_301</t>
+          <t>AB-CRPS1.2.0_113</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>跨境支付功能一期</t>
+          <t>离线支付支持</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1625,12 +1632,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>肖丽</t>
+          <t>开发02</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>跨境组</t>
+          <t>算法组</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1650,7 +1657,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1658,38 +1665,42 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr"/>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>重点需求</t>
+          <t>略有延期</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.1_302</t>
+          <t>AB-CRPS1.2.0_114</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>汇率自动转换</t>
+          <t>反洗钱监控</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1699,17 +1710,17 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>许洋</t>
+          <t>开发01</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>跨境组</t>
+          <t>运维组</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>跨境支付</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1724,42 +1735,46 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>进行中</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr"/>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
       <c r="P16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.2_303</t>
+          <t>AB-CRPS1.2.0_115</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>跨境付款申报</t>
+          <t>容灾切换</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1769,17 +1784,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>徐鹏</t>
+          <t>开发19</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>跨境组</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>跨境支付</t>
+          <t>开放平台</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1787,14 +1802,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1802,38 +1817,42 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr"/>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>监管合规</t>
+          <t>提前完成</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.2.3_304</t>
+          <t>AB-CRPS1.2.0_116</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>多币种结算支持</t>
+          <t>交易监控预警</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1843,12 +1862,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>孙浩</t>
+          <t>开发16</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>跨境组</t>
+          <t>算法组</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1868,7 +1887,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1876,32 +1895,42 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="M18" s="7" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>133</v>
+      </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr"/>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>需求变更</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.0_401</t>
+          <t>AB-CRPS1.2.0_117</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>财务对账自动化</t>
+          <t>审计日志</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1911,17 +1940,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>马超</t>
+          <t>开发11</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>运维组</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>技术重构</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1929,9 +1958,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1941,35 +1970,45 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>53</v>
+      </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>需求变更</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.1_402</t>
+          <t>AB-CRPS1.2.0_118</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>银行回单自动匹配</t>
+          <t>跨境付款申报</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1979,7 +2018,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>韩梅</t>
+          <t>开发08</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1997,47 +2036,53 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="M20" s="7" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>98</v>
+      </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr"/>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
       <c r="P20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.2_403</t>
+          <t>AB-CRPS1.2.0_119</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>账期自动清分</t>
+          <t>跨境付款申报</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2047,17 +2092,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>杨明</t>
+          <t>开发02</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>支付三组</t>
+          <t>算法组</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>风控合规</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2065,47 +2110,57 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="M21" s="4" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>143</v>
+      </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
+          <t>2025-13-19</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>2025-13-20</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>需求变更</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.3_404</t>
+          <t>AB-CRPS1.2.0_120</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>财务报表自动生成</t>
+          <t>合规检查</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -2115,17 +2170,17 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>朱磊</t>
+          <t>开发02</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>支付一组</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>风控合规</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -2133,14 +2188,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -2148,32 +2203,42 @@
           <t>优化版</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="M22" s="7" t="inlineStr"/>
+        <v>141</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>139</v>
+      </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr"/>
-      <c r="P22" s="7" t="inlineStr"/>
+          <t>2025-13-20</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>2025-13-21</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>提前完成</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.3.4_405</t>
+          <t>AB-CRPS1.3.0_121</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>发票自动开具</t>
+          <t>加解密服务</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2183,17 +2248,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>秦奋</t>
+          <t>开发11</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>支付二组</t>
+          <t>风控组</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>对公运营</t>
+          <t>算法优化</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2201,14 +2266,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2216,32 +2281,42 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" s="4" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>170</v>
+      </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr"/>
-      <c r="P23" s="4" t="inlineStr"/>
+          <t>2025-13-21</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>2025-13-22</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>提前完成</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.4.0_501</t>
+          <t>AB-CRPS1.3.0_122</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>API开放平台一期</t>
+          <t>SDK工具包</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -2251,17 +2326,17 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>尤佳</t>
+          <t>开发19</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>开放平台组</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>开放平台</t>
+          <t>企业钱包</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2284,36 +2359,38 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>71</v>
+      </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="O24" s="7" t="inlineStr"/>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>重要项目</t>
-        </is>
-      </c>
+          <t>2025-14-22</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>2025-14-23</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.4.1_502</t>
+          <t>AB-CRPS1.3.0_123</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>第三方支付接入</t>
+          <t>退款流程自动化</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2323,17 +2400,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>许珂</t>
+          <t>开发04</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>开放平台组</t>
+          <t>跨境组</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>开放平台</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2341,51 +2418,57 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M25" s="4" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>116</v>
+      </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr"/>
+          <t>2025-14-23</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>2025-14-24</t>
+        </is>
+      </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>支付宝/微信</t>
+          <t>需求变更</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.4.2_503</t>
+          <t>AB-CRPS1.3.0_124</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>SDK开发者工具包</t>
+          <t>企业钱包功能</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -2395,17 +2478,17 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>西门吹</t>
+          <t>开发06</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>开放平台组</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>开放平台</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2413,14 +2496,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -2428,32 +2511,42 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>99</v>
+      </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr"/>
-      <c r="P26" s="7" t="inlineStr"/>
+          <t>2025-14-24</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>2025-14-25</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>提前完成</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.4.3_504</t>
+          <t>AB-CRPS1.3.0_125</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>API文档自动化</t>
+          <t>密钥轮换</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2463,17 +2556,17 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>欧阳峰</t>
+          <t>开发18</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>开放平台组</t>
+          <t>移动组</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>开放平台</t>
+          <t>风控合规</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2481,47 +2574,53 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="M27" s="4" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>61</v>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr"/>
+          <t>2025-15-25</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>2025-15-26</t>
+        </is>
+      </c>
       <c r="P27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.0_601</t>
+          <t>AB-CRPS1.3.0_126</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>移动端支付优化</t>
+          <t>银企直连功能</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2531,7 +2630,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>司马光</t>
+          <t>开发05</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2541,7 +2640,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>移动支付</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -2549,9 +2648,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2561,35 +2660,41 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="M28" s="7" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>65</v>
+      </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
-      <c r="P28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>开发中</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.1_602</t>
+          <t>AB-CRPS1.3.0_127</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>APP指纹支付</t>
+          <t>成功率分析</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2599,17 +2704,17 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>诸葛亮</t>
+          <t>开发01</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>移动组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>移动支付</t>
+          <t>开放平台</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2617,14 +2722,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2632,36 +2737,34 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="M29" s="4" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>75</v>
+      </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr"/>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>生物识别</t>
-        </is>
-      </c>
+      <c r="P29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.2_603</t>
+          <t>AB-CRPS1.3.0_128</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>支付码动态更新</t>
+          <t>合规检查</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -2671,12 +2774,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>貂蝉</t>
+          <t>开发03</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>移动组</t>
+          <t>支付二组</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2689,47 +2792,53 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="M30" s="7" t="inlineStr"/>
+        <v>174</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>88</v>
+      </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
-      <c r="P30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>测试阶段</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS1.5.3_604</t>
+          <t>AB-CRPS1.3.0_129</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>离线支付支持</t>
+          <t>单点登录</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2739,17 +2848,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>吕布</t>
+          <t>开发08</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>移动组</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>移动支付</t>
+          <t>算法优化</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2757,9 +2866,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2769,39 +2878,41 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>待开发</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="M31" s="4" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>109</v>
+      </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>技术挑战大</t>
+          <t>开发中</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.0_701</t>
+          <t>AB-CRPS1.3.0_130</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>架构升级-微服务改造</t>
+          <t>电子凭证功能</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -2811,17 +2922,17 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>关羽</t>
+          <t>开发18</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>架构组</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>对公运营</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -2829,14 +2940,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
@@ -2844,36 +2955,38 @@
           <t>重构版</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="M32" s="7" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>76</v>
+      </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>重大重构</t>
+          <t>测试阶段</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.1_702</t>
+          <t>AB-CRPS2.1.0_131</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>数据库分库分表</t>
+          <t>缓存架构升级</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2883,17 +2996,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>张飞</t>
+          <t>开发09</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>架构组</t>
+          <t>支付一组</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2908,40 +3021,46 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="M33" s="4" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>86</v>
+      </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr"/>
-      <c r="P33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>需求确认中</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.2_703</t>
+          <t>AB-CRPS2.1.0_132</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>消息队列异步化</t>
+          <t>成功率分析</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -2951,17 +3070,17 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>刘备</t>
+          <t>开发02</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>架构组</t>
+          <t>开放平台组</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>技术重构</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -2969,9 +3088,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2981,39 +3100,41 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>重构版</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L34" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="M34" s="7" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>82</v>
+      </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>Kafka迁移</t>
+          <t>开发中</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.0.3_704</t>
+          <t>AB-CRPS2.1.0_133</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>缓存架构优化</t>
+          <t>离线支付支持</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3023,12 +3144,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>曹操</t>
+          <t>开发12</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>架构组</t>
+          <t>跨境组</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3053,39 +3174,41 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L35" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M35" s="4" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>107</v>
+      </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr"/>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Redis集群</t>
+          <t>需求确认中</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.0_801</t>
+          <t>AB-CRPS2.1.0_134</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>实时支付监控系统</t>
+          <t>账户管理功能</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -3095,17 +3218,17 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>孙权</t>
+          <t>开发19</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>运维组</t>
+          <t>支付三组</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>开放平台</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -3113,9 +3236,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -3128,18 +3251,20 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L36" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="M36" s="7" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
@@ -3148,12 +3273,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.1_802</t>
+          <t>AB-CRPS2.1.0_135</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>异常交易自动预警</t>
+          <t>税务申报</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3163,17 +3288,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>周瑜</t>
+          <t>开发20</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>运维组</t>
+          <t>架构组</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>风控合规</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -3181,51 +3306,49 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>常规版</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="L37" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="M37" s="4" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2027-04-15</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr"/>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>风控相关</t>
-        </is>
-      </c>
+      <c r="P37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.2_803</t>
+          <t>AB-CRPS2.1.0_136</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>支付成功率监控</t>
+          <t>实时监控系统</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -3235,17 +3358,17 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>鲁智深</t>
+          <t>开发19</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>运维组</t>
+          <t>跨境组</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>开放平台</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -3253,9 +3376,9 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -3268,18 +3391,18 @@
           <t>优化版</t>
         </is>
       </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="L38" s="7" t="n">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
@@ -3288,12 +3411,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.1.3_804</t>
+          <t>AB-CRPS2.1.0_137</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>银行通道质量分析</t>
+          <t>银行通道管理</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3303,17 +3426,17 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>武松</t>
+          <t>开发18</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>运维组</t>
+          <t>风控组</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>移动支付</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -3336,18 +3459,18 @@
           <t>优化版</t>
         </is>
       </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="K39" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="L39" s="4" t="n">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="M39" s="4" t="inlineStr"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr"/>
@@ -3356,12 +3479,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.2.0_901</t>
+          <t>AB-CRPS2.1.0_138</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>智能路由优化</t>
+          <t>退款流程自动化</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -3371,7 +3494,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>林冲</t>
+          <t>开发10</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -3396,44 +3519,40 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="L40" s="7" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
+      <c r="P40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>AB-CRPS2.2.1_902</t>
+          <t>AB-CRPS2.1.0_139</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>通道自动切换</t>
+          <t>缓存架构升级</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3443,17 +3562,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>宋江</t>
+          <t>开发04</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>算法组</t>
+          <t>移动组</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>算法优化</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -3461,14 +3580,14 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3476,18 +3595,18 @@
           <t>常规版</t>
         </is>
       </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+      <c r="K41" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="L41" s="4" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M41" s="4" t="inlineStr"/>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr"/>
@@ -3496,12 +3615,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>AB-CRPS2.2.2_903</t>
+          <t>AB-CRPS2.1.0_140</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>成本最优通道选择</t>
+          <t>数据库分库分表</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -3511,17 +3630,17 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>吴用</t>
+          <t>开发14</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>算法组</t>
+          <t>支付一组</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>算法优化</t>
+          <t>跨境支付</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -3529,37 +3648,4257 @@
           <t>AB-CRPS</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>优化版</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>规划中</t>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="L42" s="7" t="n">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>2027-07-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_141</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>批量代发优化</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>开发02</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_142</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>OAuth集成</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>开发05</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr"/>
+      <c r="P44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_143</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Token管理</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>开发17</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_144</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>支付通道接入优化</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>开发17</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_145</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>电子回单功能</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>开发10</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_146</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>单点登录</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>开发11</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_147</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>密钥轮换</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>开发06</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_148</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>数据库分库分表</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>开发17</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_149</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>企业钱包功能</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>开发16</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.2.0_150</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>合规检查</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>开发02</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_151</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>负载均衡</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>开发10</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr"/>
+      <c r="P53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_152</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>预算控制</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>开发20</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>167</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_153</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>电子凭证功能</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>开发19</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_154</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>交易追踪</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>开发15</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_155</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>合规检查</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>开发16</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_156</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>实时监控系统</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_157</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>容灾切换</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_158</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>手续费自动计算</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_159</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>流量分发</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>开发06</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS2.3.0_160</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>通道自动切换</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>开发06</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr"/>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_161</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>离线支付支持</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>开发05</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_162</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>移动端优化</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>153</v>
+      </c>
+      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_163</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>SDK工具包</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>开发02</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_164</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>SDK工具包</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>开发14</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>121</v>
+      </c>
+      <c r="M66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_165</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>跨境付款申报</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>开发08</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_166</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>财务报表生成</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>开发08</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>273</v>
+      </c>
+      <c r="M68" s="7" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_167</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>OAuth集成</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_168</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>加解密服务</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>开发06</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="M70" s="7" t="inlineStr"/>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_169</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>交易监控预警</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>开发17</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.1.0_170</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>审计日志</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>开发05</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>143</v>
+      </c>
+      <c r="M72" s="7" t="inlineStr"/>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_171</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>财务报表生成</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_172</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>网关服务重构</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>开发03</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>208</v>
+      </c>
+      <c r="M74" s="7" t="inlineStr"/>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_173</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>批量代发优化</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_174</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>预算控制</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>开发06</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="M76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_175</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>预算控制</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>开发15</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_176</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>成功率分析</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>开发05</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>255</v>
+      </c>
+      <c r="M78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr"/>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_177</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>人脸支付</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_178</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>负载均衡</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>开发03</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="M80" s="7" t="inlineStr"/>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="inlineStr"/>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_179</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>智能路由算法</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>开发03</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="O81" s="4" t="inlineStr"/>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.2.0_180</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>SDK工具包</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>开发20</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="M82" s="7" t="inlineStr"/>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_181</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>预算控制</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>开发20</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>2027-09-25</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_182</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>移动端优化</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>开发14</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="M84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>2027-10-26</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_183</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>多币种结算</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="M85" s="4" t="inlineStr"/>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>2027-11-27</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr"/>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_184</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>成本优化</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>开发13</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="M86" s="7" t="inlineStr"/>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>2027-12-28</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr"/>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_185</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>离线支付支持</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>技术重构</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="M87" s="4" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_186</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>权限管理</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>开发10</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>风控合规</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="n">
+        <v>251</v>
+      </c>
+      <c r="M88" s="7" t="inlineStr"/>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr"/>
+      <c r="P88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_187</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>缓存架构升级</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>开发13</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M89" s="4" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr"/>
+      <c r="P89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_188</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>异常交易预警</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>开发10</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L90" s="7" t="n">
+        <v>271</v>
+      </c>
+      <c r="M90" s="7" t="inlineStr"/>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>2027-04-04</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr"/>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_189</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>密钥轮换</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>开发15</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>2027-05-05</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS3.3.0_190</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>支付通道接入优化</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>开发10</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L92" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="M92" s="7" t="inlineStr"/>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>2027-06-06</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr"/>
+      <c r="P92" s="7" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_191</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>交易追踪</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>开发11</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>开放平台</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="M93" s="4" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>2027-07-07</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr"/>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_192</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>负载均衡</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>开发01</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>企业钱包</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L94" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="M94" s="7" t="inlineStr"/>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>2027-08-08</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr"/>
+      <c r="P94" s="7" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_193</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>反洗钱监控</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>开发14</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr"/>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_194</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>API开放接口</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>开发19</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L96" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="M96" s="7" t="inlineStr"/>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>2027-10-10</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr"/>
+      <c r="P96" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_195</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>离线支付支持</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>开发04</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>移动支付</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="M97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>2027-11-11</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="inlineStr"/>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>资源待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_196</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>指纹支付</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>开发09</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>跨境支付</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>294</v>
+      </c>
+      <c r="M98" s="7" t="inlineStr"/>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>2027-12-12</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr"/>
+      <c r="P98" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_197</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>密钥轮换</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>开发12</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>常规版</t>
+        </is>
+      </c>
+      <c r="K99" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="M99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr"/>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>待立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_198</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>税务申报</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>开发18</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>对公运营</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>重构版</t>
+        </is>
+      </c>
+      <c r="K100" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="M100" s="7" t="inlineStr"/>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>2027-02-14</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr"/>
+      <c r="P100" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_199</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>离线支付支持</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>开发04</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>2027-03-15</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr"/>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS4.1.0_200</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>实时监控系统</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>田家喜</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>开发13</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>算法优化</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>AB-CRPS</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>优化版</t>
+        </is>
+      </c>
+      <c r="K102" s="13" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="n">
+        <v>285</v>
+      </c>
+      <c r="M102" s="7" t="inlineStr"/>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>2027-04-16</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr"/>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>技术方案评审中</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3575,269 +7914,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>AB-CRPS系统需求统计分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>【基本统计】</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>【优先级分布】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>数量/工时</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>总需求数</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>总预估工时</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14146</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>已完成工时</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>【状态分布】</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>【团队分布】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>预估工时</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>团队</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>需求数</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>预估工时</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>支付一组</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2119</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>支付二组</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1811</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>支付三组</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>40</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2448</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>跨境组</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>开放平台组</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>移动组</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>架构组</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>运维组</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>算法组</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>风控组</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>780</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>需求统计汇总</t>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>工时统计分析</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>状态分布</t>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>总工时</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>平均工时</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>最大工时</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>最小工时</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>预估工时</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14146</v>
+      </c>
+      <c r="C4" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" t="n">
+        <v>294</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>实际工时</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>3201</v>
       </c>
       <c r="C5" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>规划中</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>优先级分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>团队分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>团队</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>需求数</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>支付一组</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>支付二组</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>支付三组</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>跨境组</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>开放平台组</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>移动组</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>架构组</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>运维组</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>算法组</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
+        <v>91</v>
+      </c>
+      <c r="D5" t="n">
+        <v>170</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>